--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,13 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
   </si>
 </sst>
 </file>
@@ -658,16 +667,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68.18000000000001</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -681,16 +693,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -704,16 +719,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -750,16 +768,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>90.48</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -815,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>54.55</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -850,7 +871,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -867,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>87.09999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -928,7 +949,7 @@
         <v>90.48</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -938,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -970,24 +991,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920192</v>
+        <v>22330051920043</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920045</v>
+      </c>
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -745,16 +745,19 @@
         <v>21</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>21</v>
       </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -923,7 +926,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -1012,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -82,16 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PALOMINO</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>DE JESUS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
@@ -962,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -994,7 +1000,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920043</v>
+        <v>23330051920203</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1003,21 +1009,21 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920045</v>
+        <v>22330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1026,7 +1032,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1035,6 +1041,29 @@
         <v>13</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920045</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,39 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>PALOMINO</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -95,6 +122,21 @@
   </si>
   <si>
     <t>ROMERO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
@@ -968,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,16 +1042,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920203</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1018,52 +1060,167 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920043</v>
+        <v>23330051920189</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
+        <v>23330051920195</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920202</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920359</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920203</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920043</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>22330051920045</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G4">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -94,12 +94,15 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>PALOMINO</t>
   </si>
   <si>
@@ -112,12 +115,15 @@
     <t>MIRON</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>TIZA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -136,10 +142,13 @@
     <t>LAZARO</t>
   </si>
   <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
     <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
@@ -569,10 +578,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -581,7 +590,7 @@
         <v>27</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
         <v>8.800000000000001</v>
@@ -621,10 +630,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -633,7 +642,7 @@
         <v>21</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -647,10 +656,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -659,7 +668,7 @@
         <v>19</v>
       </c>
       <c r="G6">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="H6">
         <v>7.4</v>
@@ -738,10 +747,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -750,7 +759,7 @@
         <v>27</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
         <v>8.800000000000001</v>
@@ -790,10 +799,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -802,7 +811,7 @@
         <v>21</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -816,10 +825,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -828,7 +837,7 @@
         <v>19</v>
       </c>
       <c r="G6">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="H6">
         <v>7.4</v>
@@ -907,10 +916,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -919,7 +928,7 @@
         <v>27</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
         <v>8.300000000000001</v>
@@ -959,10 +968,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -971,7 +980,7 @@
         <v>21</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -985,10 +994,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -997,7 +1006,7 @@
         <v>19</v>
       </c>
       <c r="G6">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -1010,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1048,10 +1057,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1071,10 +1080,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1094,10 +1103,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1120,7 +1129,7 @@
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1134,16 +1143,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920359</v>
+        <v>22330051920356</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1163,10 +1172,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1180,22 +1189,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920043</v>
+        <v>22330051920359</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1203,16 +1212,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920045</v>
+        <v>22330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1221,6 +1230,29 @@
         <v>13</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920045</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -82,79 +82,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
     <t>MIRON</t>
   </si>
   <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>TIZA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
     <t>BRAYAN</t>
   </si>
   <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
     <t>JOSUE GUSTAVO</t>
   </si>
   <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
     <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
   </si>
 </sst>
 </file>
@@ -896,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>68.18000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -922,16 +874,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>93.09999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -948,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -1019,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1051,16 +1003,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920183</v>
+        <v>23330051920195</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1069,190 +1021,52 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920189</v>
+        <v>22330051920356</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920195</v>
+        <v>22330051920359</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920202</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920356</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920203</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920359</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920043</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920045</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -85,28 +85,10 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MIRON</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
   </si>
 </sst>
 </file>
@@ -533,19 +515,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>93.09999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -585,19 +567,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -611,19 +593,19 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -702,19 +684,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>93.09999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -754,19 +736,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -780,19 +762,19 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -871,19 +853,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -923,16 +905,16 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -949,16 +931,16 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>86.36</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -971,7 +953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1009,10 +991,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1021,53 +1003,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920356</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920359</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
